--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/121.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/121.xlsx
@@ -426,13 +426,13 @@
         <v>-23.90116976637442</v>
       </c>
       <c r="E2">
-        <v>-13.16417186210315</v>
+        <v>-15.41421209992429</v>
       </c>
       <c r="F2">
-        <v>-3.452024975339984</v>
+        <v>-3.195552487024423</v>
       </c>
       <c r="G2">
-        <v>-11.02414097026016</v>
+        <v>-11.14743892832478</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-24.07245570759222</v>
       </c>
       <c r="E3">
-        <v>-15.01167151690846</v>
+        <v>-16.62549285596996</v>
       </c>
       <c r="F3">
-        <v>-3.590057492403271</v>
+        <v>-3.694965253763412</v>
       </c>
       <c r="G3">
-        <v>-11.22208179859873</v>
+        <v>-10.3307803125152</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-24.11159789274864</v>
       </c>
       <c r="E4">
-        <v>-13.15736103719562</v>
+        <v>-16.17987289971917</v>
       </c>
       <c r="F4">
-        <v>-3.361037099816486</v>
+        <v>-3.491900097008544</v>
       </c>
       <c r="G4">
-        <v>-10.2467752194562</v>
+        <v>-10.10488523764304</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-23.96114427719305</v>
       </c>
       <c r="E5">
-        <v>-14.991913784813</v>
+        <v>-16.83123048708644</v>
       </c>
       <c r="F5">
-        <v>-3.512066701429698</v>
+        <v>-3.169248508515928</v>
       </c>
       <c r="G5">
-        <v>-10.58018357126174</v>
+        <v>-10.56956334117176</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.62224624154412</v>
       </c>
       <c r="E6">
-        <v>-14.74353151396628</v>
+        <v>-17.29753198413027</v>
       </c>
       <c r="F6">
-        <v>-3.818973510697303</v>
+        <v>-2.936370408934306</v>
       </c>
       <c r="G6">
-        <v>-10.20769753991064</v>
+        <v>-10.41427558156116</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-23.05422889079443</v>
       </c>
       <c r="E7">
-        <v>-15.91808181733574</v>
+        <v>-18.16349395472104</v>
       </c>
       <c r="F7">
-        <v>-3.584481751415028</v>
+        <v>-2.920496404394459</v>
       </c>
       <c r="G7">
-        <v>-9.615063540743549</v>
+        <v>-10.02192627697444</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.27651530724545</v>
       </c>
       <c r="E8">
-        <v>-16.64929904382829</v>
+        <v>-18.1931690448933</v>
       </c>
       <c r="F8">
-        <v>-2.968962524397452</v>
+        <v>-2.964125687132506</v>
       </c>
       <c r="G8">
-        <v>-10.01042213122547</v>
+        <v>-9.491603365947508</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.30127209492658</v>
       </c>
       <c r="E9">
-        <v>-15.67872479518632</v>
+        <v>-18.07312372742397</v>
       </c>
       <c r="F9">
-        <v>-3.680907030570501</v>
+        <v>-3.11171176545228</v>
       </c>
       <c r="G9">
-        <v>-10.0214760427811</v>
+        <v>-9.796670137391349</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-20.12900532970266</v>
       </c>
       <c r="E10">
-        <v>-17.33130534327947</v>
+        <v>-19.11839515482245</v>
       </c>
       <c r="F10">
-        <v>-3.222730393142872</v>
+        <v>-3.181616033839724</v>
       </c>
       <c r="G10">
-        <v>-8.959436481055205</v>
+        <v>-8.808296835005317</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.81412431395743</v>
       </c>
       <c r="E11">
-        <v>-17.64052313394523</v>
+        <v>-19.70685223822319</v>
       </c>
       <c r="F11">
-        <v>-3.320609457090259</v>
+        <v>-2.99424926773531</v>
       </c>
       <c r="G11">
-        <v>-9.437499120199199</v>
+        <v>-8.788069401760371</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.39853708269957</v>
       </c>
       <c r="E12">
-        <v>-18.75151177614303</v>
+        <v>-20.37353418163242</v>
       </c>
       <c r="F12">
-        <v>-2.285075650524625</v>
+        <v>-3.30735640701287</v>
       </c>
       <c r="G12">
-        <v>-8.8570711024354</v>
+        <v>-8.271961973279071</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.91519024026598</v>
       </c>
       <c r="E13">
-        <v>-18.41723341031882</v>
+        <v>-20.59294327577805</v>
       </c>
       <c r="F13">
-        <v>-2.968771171527405</v>
+        <v>-3.034810277613388</v>
       </c>
       <c r="G13">
-        <v>-7.628749459362993</v>
+        <v>-8.129777352912912</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.44846123252973</v>
       </c>
       <c r="E14">
-        <v>-19.52234409325467</v>
+        <v>-21.39209214085966</v>
       </c>
       <c r="F14">
-        <v>-2.96591993092697</v>
+        <v>-2.989193741476024</v>
       </c>
       <c r="G14">
-        <v>-8.250781102918813</v>
+        <v>-8.114446216520548</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.04655255142673</v>
       </c>
       <c r="E15">
-        <v>-20.53173642109038</v>
+        <v>-21.69984723442094</v>
       </c>
       <c r="F15">
-        <v>-3.076763773095572</v>
+        <v>-2.680328671668201</v>
       </c>
       <c r="G15">
-        <v>-7.43262280997995</v>
+        <v>-7.676864928230761</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.75587069114803</v>
       </c>
       <c r="E16">
-        <v>-21.50041323912313</v>
+        <v>-23.10129672794472</v>
       </c>
       <c r="F16">
-        <v>-2.735904669089423</v>
+        <v>-2.637492964902036</v>
       </c>
       <c r="G16">
-        <v>-7.767792372012384</v>
+        <v>-6.831364839683057</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.63774966036486</v>
       </c>
       <c r="E17">
-        <v>-21.12914176913027</v>
+        <v>-23.40866237274134</v>
       </c>
       <c r="F17">
-        <v>-3.084902482828077</v>
+        <v>-2.623488585590307</v>
       </c>
       <c r="G17">
-        <v>-6.724219033304545</v>
+        <v>-6.864159103795077</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.702773001205136</v>
       </c>
       <c r="E18">
-        <v>-21.89573090609672</v>
+        <v>-23.69684087316746</v>
       </c>
       <c r="F18">
-        <v>-2.528875774312159</v>
+        <v>-2.815073398509777</v>
       </c>
       <c r="G18">
-        <v>-5.145545666356608</v>
+        <v>-6.072117704615525</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.966644573635906</v>
       </c>
       <c r="E19">
-        <v>-22.57928141518452</v>
+        <v>-23.95732775503667</v>
       </c>
       <c r="F19">
-        <v>-2.640254741822969</v>
+        <v>-2.848639674038616</v>
       </c>
       <c r="G19">
-        <v>-6.038965901585263</v>
+        <v>-5.941563030728825</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.440932788096649</v>
       </c>
       <c r="E20">
-        <v>-23.93540088389153</v>
+        <v>-25.22501518332189</v>
       </c>
       <c r="F20">
-        <v>-2.247823968420732</v>
+        <v>-2.018086209663122</v>
       </c>
       <c r="G20">
-        <v>-6.074468191948407</v>
+        <v>-5.253211228384785</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.096442827569845</v>
       </c>
       <c r="E21">
-        <v>-24.31238275960806</v>
+        <v>-25.87874116259517</v>
       </c>
       <c r="F21">
-        <v>-1.827942756024524</v>
+        <v>-2.11865249746519</v>
       </c>
       <c r="G21">
-        <v>-6.353116809988863</v>
+        <v>-5.595660680058075</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.930725364674186</v>
       </c>
       <c r="E22">
-        <v>-23.93340382685415</v>
+        <v>-26.9933480555251</v>
       </c>
       <c r="F22">
-        <v>-2.008734770052918</v>
+        <v>-1.749434235424201</v>
       </c>
       <c r="G22">
-        <v>-4.276818790305377</v>
+        <v>-5.241657424452729</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.926990961366957</v>
       </c>
       <c r="E23">
-        <v>-24.86225724446344</v>
+        <v>-26.62702620762262</v>
       </c>
       <c r="F23">
-        <v>-2.221396563169219</v>
+        <v>-1.799102316528656</v>
       </c>
       <c r="G23">
-        <v>-5.861494176316013</v>
+        <v>-5.174774472922834</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.039967204023064</v>
       </c>
       <c r="E24">
-        <v>-26.83931201215419</v>
+        <v>-26.61487631186004</v>
       </c>
       <c r="F24">
-        <v>-1.36379358962271</v>
+        <v>-1.384381004684486</v>
       </c>
       <c r="G24">
-        <v>-5.519978298484797</v>
+        <v>-5.368484424062208</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.253766647605921</v>
       </c>
       <c r="E25">
-        <v>-27.18383831465775</v>
+        <v>-27.42662339163098</v>
       </c>
       <c r="F25">
-        <v>-1.717698651855549</v>
+        <v>-1.755212098058727</v>
       </c>
       <c r="G25">
-        <v>-4.322444728927612</v>
+        <v>-5.563806610879208</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.532374449474753</v>
       </c>
       <c r="E26">
-        <v>-27.6366902438988</v>
+        <v>-28.42093137254715</v>
       </c>
       <c r="F26">
-        <v>-1.122600338051787</v>
+        <v>-1.123490833009796</v>
       </c>
       <c r="G26">
-        <v>-4.270290394501934</v>
+        <v>-5.781143925532362</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.83153624055929</v>
       </c>
       <c r="E27">
-        <v>-25.87174919872733</v>
+        <v>-28.39111589968065</v>
       </c>
       <c r="F27">
-        <v>-1.929666273088303</v>
+        <v>-1.39496919682707</v>
       </c>
       <c r="G27">
-        <v>-6.251499614660934</v>
+        <v>-6.382054288547632</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.142611716631082</v>
       </c>
       <c r="E28">
-        <v>-28.52997249817784</v>
+        <v>-28.80488256976149</v>
       </c>
       <c r="F28">
-        <v>-1.310444243780214</v>
+        <v>-1.589753164656151</v>
       </c>
       <c r="G28">
-        <v>-5.222409912687406</v>
+        <v>-5.717362955172763</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.441127194444821</v>
       </c>
       <c r="E29">
-        <v>-25.78037365020056</v>
+        <v>-28.13862177443497</v>
       </c>
       <c r="F29">
-        <v>-1.769957037828558</v>
+        <v>-1.473796638877471</v>
       </c>
       <c r="G29">
-        <v>-4.415533958946379</v>
+        <v>-6.017361281395979</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.711426298128089</v>
       </c>
       <c r="E30">
-        <v>-26.80836442078577</v>
+        <v>-29.16240559266706</v>
       </c>
       <c r="F30">
-        <v>-1.252243978426923</v>
+        <v>-1.444947087340172</v>
       </c>
       <c r="G30">
-        <v>-5.357943647065169</v>
+        <v>-5.910328033565802</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.960837752986709</v>
       </c>
       <c r="E31">
-        <v>-26.64751755250733</v>
+        <v>-27.40995860728276</v>
       </c>
       <c r="F31">
-        <v>-1.195773344210678</v>
+        <v>-1.464928137463099</v>
       </c>
       <c r="G31">
-        <v>-6.596597502765641</v>
+        <v>-5.560025967873361</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.1790263727842</v>
       </c>
       <c r="E32">
-        <v>-26.89148908967057</v>
+        <v>-27.17932795454611</v>
       </c>
       <c r="F32">
-        <v>-1.652298217037125</v>
+        <v>-1.179022926958669</v>
       </c>
       <c r="G32">
-        <v>-5.568216257537517</v>
+        <v>-6.362584970231178</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.36950610991102</v>
       </c>
       <c r="E33">
-        <v>-24.88835936864366</v>
+        <v>-27.09042948130154</v>
       </c>
       <c r="F33">
-        <v>-1.582939014400722</v>
+        <v>-1.276381776177098</v>
       </c>
       <c r="G33">
-        <v>-4.852956341050281</v>
+        <v>-6.428772707197827</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.5438937489408</v>
       </c>
       <c r="E34">
-        <v>-27.76461963461549</v>
+        <v>-27.66360296492638</v>
       </c>
       <c r="F34">
-        <v>-1.630434287807635</v>
+        <v>-1.068930414024407</v>
       </c>
       <c r="G34">
-        <v>-5.533763410110322</v>
+        <v>-5.644713033313457</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.69313470703293</v>
       </c>
       <c r="E35">
-        <v>-26.56970025515952</v>
+        <v>-26.89128530834023</v>
       </c>
       <c r="F35">
-        <v>-1.227780632287448</v>
+        <v>-1.208813503865548</v>
       </c>
       <c r="G35">
-        <v>-6.448957103350764</v>
+        <v>-6.73673289544299</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.82976260240881</v>
       </c>
       <c r="E36">
-        <v>-26.29165647956257</v>
+        <v>-26.58651447915</v>
       </c>
       <c r="F36">
-        <v>-1.105449819344226</v>
+        <v>-1.325636501947557</v>
       </c>
       <c r="G36">
-        <v>-6.531935927292595</v>
+        <v>-6.254290404550539</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.9608192419756</v>
       </c>
       <c r="E37">
-        <v>-24.57867061668111</v>
+        <v>-27.12006381520773</v>
       </c>
       <c r="F37">
-        <v>-1.186411135824238</v>
+        <v>-1.026981060379237</v>
       </c>
       <c r="G37">
-        <v>-6.039909407063955</v>
+        <v>-6.349293129891004</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.0734992685931</v>
       </c>
       <c r="E38">
-        <v>-26.23569359777578</v>
+        <v>-25.29560050767945</v>
       </c>
       <c r="F38">
-        <v>-0.8780629672757613</v>
+        <v>-1.276217759431344</v>
       </c>
       <c r="G38">
-        <v>-4.660037610294792</v>
+        <v>-6.27204817082319</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.18049818476741</v>
       </c>
       <c r="E39">
-        <v>-25.08216899922393</v>
+        <v>-26.07509126709375</v>
       </c>
       <c r="F39">
-        <v>-1.384491177549059</v>
+        <v>-1.154407161217079</v>
       </c>
       <c r="G39">
-        <v>-5.979816384435104</v>
+        <v>-6.189251426886018</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.27991656323296</v>
       </c>
       <c r="E40">
-        <v>-24.87453846597225</v>
+        <v>-25.44079696978738</v>
       </c>
       <c r="F40">
-        <v>-0.9567901768704236</v>
+        <v>-1.309405471057103</v>
       </c>
       <c r="G40">
-        <v>-6.390658396404198</v>
+        <v>-6.228464838798685</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.3569309004806</v>
       </c>
       <c r="E41">
-        <v>-22.88604477293812</v>
+        <v>-24.21477603084674</v>
       </c>
       <c r="F41">
-        <v>-1.245412432456036</v>
+        <v>-1.085647696580303</v>
       </c>
       <c r="G41">
-        <v>-5.659987890431654</v>
+        <v>-6.409829765622117</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.42292671993746</v>
       </c>
       <c r="E42">
-        <v>-24.48704600208391</v>
+        <v>-24.14919919874166</v>
       </c>
       <c r="F42">
-        <v>-1.298490902157817</v>
+        <v>-0.8205502468667945</v>
       </c>
       <c r="G42">
-        <v>-6.057677104973223</v>
+        <v>-6.416497204338209</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.46859984429089</v>
       </c>
       <c r="E43">
-        <v>-21.09520538491679</v>
+        <v>-23.91476915631258</v>
       </c>
       <c r="F43">
-        <v>-0.8621036408934261</v>
+        <v>-1.156029932959163</v>
       </c>
       <c r="G43">
-        <v>-5.882042732478269</v>
+        <v>-6.550620646316243</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.48371077116802</v>
       </c>
       <c r="E44">
-        <v>-24.21235782572664</v>
+        <v>-23.0659791591589</v>
       </c>
       <c r="F44">
-        <v>-1.508535882648673</v>
+        <v>-1.115956003113932</v>
       </c>
       <c r="G44">
-        <v>-5.640406013566865</v>
+        <v>-6.875027624800504</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.47814938160548</v>
       </c>
       <c r="E45">
-        <v>-22.15280331856415</v>
+        <v>-22.71240496558801</v>
       </c>
       <c r="F45">
-        <v>-1.344033713596331</v>
+        <v>-1.074164867642697</v>
       </c>
       <c r="G45">
-        <v>-6.197974714381997</v>
+        <v>-6.571828001040814</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.44033635697895</v>
       </c>
       <c r="E46">
-        <v>-20.21929888540517</v>
+        <v>-22.6042378354408</v>
       </c>
       <c r="F46">
-        <v>-1.684515082066803</v>
+        <v>-0.9595768048134411</v>
       </c>
       <c r="G46">
-        <v>-5.677927736708964</v>
+        <v>-6.62553167077887</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.36993715247528</v>
       </c>
       <c r="E47">
-        <v>-19.80763342726389</v>
+        <v>-21.72022989592946</v>
       </c>
       <c r="F47">
-        <v>-0.9409219709023962</v>
+        <v>-0.796187961550461</v>
       </c>
       <c r="G47">
-        <v>-6.42457824599957</v>
+        <v>-6.380312941593975</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.27592216194193</v>
       </c>
       <c r="E48">
-        <v>-19.40231688968136</v>
+        <v>-21.49515568080023</v>
       </c>
       <c r="F48">
-        <v>-1.066589447744095</v>
+        <v>-1.085224400837473</v>
       </c>
       <c r="G48">
-        <v>-5.659603867149099</v>
+        <v>-6.905769350678177</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.14613048092503</v>
       </c>
       <c r="E49">
-        <v>-20.62062130891293</v>
+        <v>-21.1153435088289</v>
       </c>
       <c r="F49">
-        <v>-1.652501167050811</v>
+        <v>-1.020127148488474</v>
       </c>
       <c r="G49">
-        <v>-5.282949858964058</v>
+        <v>-6.505941523718239</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.98937082748779</v>
       </c>
       <c r="E50">
-        <v>-17.87243081635203</v>
+        <v>-20.54525391600328</v>
       </c>
       <c r="F50">
-        <v>-0.8545654975279505</v>
+        <v>-1.049691581094388</v>
       </c>
       <c r="G50">
-        <v>-6.988715069164616</v>
+        <v>-6.758761265461301</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.81250196830607</v>
       </c>
       <c r="E51">
-        <v>-20.27142162123346</v>
+        <v>-19.75216414914394</v>
       </c>
       <c r="F51">
-        <v>-1.000996003320819</v>
+        <v>-1.030523159393608</v>
       </c>
       <c r="G51">
-        <v>-7.210038280647052</v>
+        <v>-7.295486771561181</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.60468587237381</v>
       </c>
       <c r="E52">
-        <v>-18.4869447391929</v>
+        <v>-19.21483806576381</v>
       </c>
       <c r="F52">
-        <v>-1.014853761602252</v>
+        <v>-0.9822989226722315</v>
       </c>
       <c r="G52">
-        <v>-6.519819330618863</v>
+        <v>-6.977244028871041</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.38178824967005</v>
       </c>
       <c r="E53">
-        <v>-17.62943742957445</v>
+        <v>-18.39499860294116</v>
       </c>
       <c r="F53">
-        <v>-0.9471744880587268</v>
+        <v>-1.197211390021938</v>
       </c>
       <c r="G53">
-        <v>-6.008492329896272</v>
+        <v>-6.626620840261291</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.1482432629203</v>
       </c>
       <c r="E54">
-        <v>-17.70205603876145</v>
+        <v>-18.33546275516232</v>
       </c>
       <c r="F54">
-        <v>-1.211068319935968</v>
+        <v>-1.1602720024289</v>
       </c>
       <c r="G54">
-        <v>-7.078003792904299</v>
+        <v>-6.776456131368705</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.896805424652054</v>
       </c>
       <c r="E55">
-        <v>-16.96857004679107</v>
+        <v>-18.11351771557239</v>
       </c>
       <c r="F55">
-        <v>-1.32849602622202</v>
+        <v>-1.075342806089478</v>
       </c>
       <c r="G55">
-        <v>-5.754997236863198</v>
+        <v>-6.79982858287596</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.646923713435291</v>
       </c>
       <c r="E56">
-        <v>-15.32481549453887</v>
+        <v>-18.11319166544384</v>
       </c>
       <c r="F56">
-        <v>-0.8153315322291576</v>
+        <v>-1.31063559665026</v>
       </c>
       <c r="G56">
-        <v>-6.894142714744256</v>
+        <v>-7.05896815605349</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.399622431838942</v>
       </c>
       <c r="E57">
-        <v>-16.9056514289285</v>
+        <v>-17.74776192692087</v>
       </c>
       <c r="F57">
-        <v>-1.520982102875736</v>
+        <v>-1.454785606983222</v>
       </c>
       <c r="G57">
-        <v>-7.963415818473457</v>
+        <v>-6.945648182244238</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.153601738007403</v>
       </c>
       <c r="E58">
-        <v>-15.35003909476159</v>
+        <v>-17.59916005235916</v>
       </c>
       <c r="F58">
-        <v>-1.808353523683121</v>
+        <v>-1.349924234197638</v>
       </c>
       <c r="G58">
-        <v>-7.406151687847938</v>
+        <v>-6.634893893563929</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.927030427261716</v>
       </c>
       <c r="E59">
-        <v>-16.22205110662661</v>
+        <v>-17.50126350126135</v>
       </c>
       <c r="F59">
-        <v>-1.767882805851948</v>
+        <v>-1.24957994885952</v>
       </c>
       <c r="G59">
-        <v>-7.262374695077391</v>
+        <v>-7.436760991904039</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.715767231861749</v>
       </c>
       <c r="E60">
-        <v>-15.00940275143062</v>
+        <v>-16.99498916415182</v>
       </c>
       <c r="F60">
-        <v>-1.858463952980671</v>
+        <v>-1.29171568517032</v>
       </c>
       <c r="G60">
-        <v>-6.347704068032154</v>
+        <v>-7.673564314328107</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.521116786127104</v>
       </c>
       <c r="E61">
-        <v>-14.8693506357954</v>
+        <v>-16.66389884402901</v>
       </c>
       <c r="F61">
-        <v>-1.719348759721925</v>
+        <v>-0.8709356941420744</v>
       </c>
       <c r="G61">
-        <v>-6.480672129616981</v>
+        <v>-7.56235646857291</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.351188687007339</v>
       </c>
       <c r="E62">
-        <v>-15.87682741912587</v>
+        <v>-16.04866489382093</v>
       </c>
       <c r="F62">
-        <v>-0.8623678900949191</v>
+        <v>-1.201115485591332</v>
       </c>
       <c r="G62">
-        <v>-7.565872267935616</v>
+        <v>-8.010961873508469</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.193141845035585</v>
       </c>
       <c r="E63">
-        <v>-15.79300083676988</v>
+        <v>-16.65644044733838</v>
       </c>
       <c r="F63">
-        <v>-0.9753712860826192</v>
+        <v>-1.390036268943398</v>
       </c>
       <c r="G63">
-        <v>-6.312092529666214</v>
+        <v>-7.644222949213547</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.050113518530345</v>
       </c>
       <c r="E64">
-        <v>-13.23826675381666</v>
+        <v>-16.5547852628142</v>
       </c>
       <c r="F64">
-        <v>-1.404886411373385</v>
+        <v>-1.532566821003887</v>
       </c>
       <c r="G64">
-        <v>-6.18569921152238</v>
+        <v>-7.032450686283928</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.924308521263695</v>
       </c>
       <c r="E65">
-        <v>-13.39268771747822</v>
+        <v>-15.68882782069743</v>
       </c>
       <c r="F65">
-        <v>-1.401365849911487</v>
+        <v>-1.318252434919002</v>
       </c>
       <c r="G65">
-        <v>-6.979227045649065</v>
+        <v>-8.276749022128858</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.80189416078582</v>
       </c>
       <c r="E66">
-        <v>-15.38728579347468</v>
+        <v>-16.38138546458649</v>
       </c>
       <c r="F66">
-        <v>-1.529069453829268</v>
+        <v>-1.198119280695406</v>
       </c>
       <c r="G66">
-        <v>-7.631321753247007</v>
+        <v>-7.435019644950382</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.691788102664907</v>
       </c>
       <c r="E67">
-        <v>-12.57537061467784</v>
+        <v>-14.50761160358868</v>
       </c>
       <c r="F67">
-        <v>-1.74135019794028</v>
+        <v>-1.637686644419144</v>
       </c>
       <c r="G67">
-        <v>-6.902793170238372</v>
+        <v>-8.012666804461194</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.594125434684034</v>
       </c>
       <c r="E68">
-        <v>-15.10488562588235</v>
+        <v>-16.0704921385379</v>
       </c>
       <c r="F68">
-        <v>-1.577678053025543</v>
+        <v>-1.559791944064296</v>
       </c>
       <c r="G68">
-        <v>-7.250029670761448</v>
+        <v>-7.643901826296237</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.499008448204361</v>
       </c>
       <c r="E69">
-        <v>-12.11896836181478</v>
+        <v>-14.76483798417237</v>
       </c>
       <c r="F69">
-        <v>-1.49053545898584</v>
+        <v>-1.340851126034775</v>
       </c>
       <c r="G69">
-        <v>-7.691232695871197</v>
+        <v>-7.802480268172867</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.41851684817657</v>
       </c>
       <c r="E70">
-        <v>-13.8302696323654</v>
+        <v>-15.61236453707792</v>
       </c>
       <c r="F70">
-        <v>-1.533146678185847</v>
+        <v>-1.650011923005398</v>
       </c>
       <c r="G70">
-        <v>-6.643282815960442</v>
+        <v>-8.411653752854157</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.349909016984495</v>
       </c>
       <c r="E71">
-        <v>-13.27417755269748</v>
+        <v>-14.69293940235259</v>
       </c>
       <c r="F71">
-        <v>-1.901233390354613</v>
+        <v>-1.553317424444015</v>
       </c>
       <c r="G71">
-        <v>-6.528751182483817</v>
+        <v>-7.48804134230735</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.286444251088222</v>
       </c>
       <c r="E72">
-        <v>-14.98517541548958</v>
+        <v>-15.50680580795912</v>
       </c>
       <c r="F72">
-        <v>-1.18149394692122</v>
+        <v>-1.818566465392236</v>
       </c>
       <c r="G72">
-        <v>-6.134554593486179</v>
+        <v>-7.474689912147469</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.237604887703517</v>
       </c>
       <c r="E73">
-        <v>-12.62726692680574</v>
+        <v>-15.87723045331255</v>
       </c>
       <c r="F73">
-        <v>-2.028068036866856</v>
+        <v>-1.620842621650619</v>
       </c>
       <c r="G73">
-        <v>-6.907484213267519</v>
+        <v>-7.56676280468568</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.195511617772021</v>
       </c>
       <c r="E74">
-        <v>-13.73585547777948</v>
+        <v>-15.94122231951494</v>
       </c>
       <c r="F74">
-        <v>-1.514838930216575</v>
+        <v>-2.074367147744126</v>
       </c>
       <c r="G74">
-        <v>-6.262957412772351</v>
+        <v>-7.61118370473162</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.157579513807599</v>
       </c>
       <c r="E75">
-        <v>-14.18447781229736</v>
+        <v>-16.62993076049748</v>
       </c>
       <c r="F75">
-        <v>-1.747416332430981</v>
+        <v>-1.740025638463204</v>
       </c>
       <c r="G75">
-        <v>-5.670147954691678</v>
+        <v>-6.970106492688373</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.129702675306262</v>
       </c>
       <c r="E76">
-        <v>-13.10783311697373</v>
+        <v>-16.37999069459213</v>
       </c>
       <c r="F76">
-        <v>-2.538633942317137</v>
+        <v>-1.978129907989088</v>
       </c>
       <c r="G76">
-        <v>-6.78878791350249</v>
+        <v>-7.099528960000641</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.101624906925723</v>
       </c>
       <c r="E77">
-        <v>-16.07714446685517</v>
+        <v>-15.79108529226464</v>
       </c>
       <c r="F77">
-        <v>-2.353356318802583</v>
+        <v>-1.760933631709863</v>
       </c>
       <c r="G77">
-        <v>-6.158625570102219</v>
+        <v>-7.212464910527338</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.076057802581957</v>
       </c>
       <c r="E78">
-        <v>-14.47458997112475</v>
+        <v>-16.94607711639497</v>
       </c>
       <c r="F78">
-        <v>-2.481805453382882</v>
+        <v>-1.948046089021618</v>
       </c>
       <c r="G78">
-        <v>-5.899270811464636</v>
+        <v>-6.940162608285665</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.056552158886221</v>
       </c>
       <c r="E79">
-        <v>-15.79663267292403</v>
+        <v>-17.93426260045277</v>
       </c>
       <c r="F79">
-        <v>-2.172856718467376</v>
+        <v>-2.292673436343102</v>
       </c>
       <c r="G79">
-        <v>-6.460577118193605</v>
+        <v>-6.83562220124656</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.0322797039273</v>
       </c>
       <c r="E80">
-        <v>-16.22706865582711</v>
+        <v>-18.65859654645364</v>
       </c>
       <c r="F80">
-        <v>-2.387577832947036</v>
+        <v>-2.35619016368756</v>
       </c>
       <c r="G80">
-        <v>-6.496655443480583</v>
+        <v>-6.599802110847655</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.011925577242298</v>
       </c>
       <c r="E81">
-        <v>-15.82081019565099</v>
+        <v>-18.22472345177875</v>
       </c>
       <c r="F81">
-        <v>-2.575076309468496</v>
+        <v>-2.353480573913003</v>
       </c>
       <c r="G81">
-        <v>-5.360191507486334</v>
+        <v>-7.326029864706497</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.996889553604248</v>
       </c>
       <c r="E82">
-        <v>-16.77519062124152</v>
+        <v>-18.40664583808889</v>
       </c>
       <c r="F82">
-        <v>-2.815095764429652</v>
+        <v>-2.31115762656917</v>
       </c>
       <c r="G82">
-        <v>-6.218890741099112</v>
+        <v>-6.846110009514971</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.978632995344745</v>
       </c>
       <c r="E83">
-        <v>-17.81469277275423</v>
+        <v>-20.1050726570357</v>
       </c>
       <c r="F83">
-        <v>-2.858099629778586</v>
+        <v>-2.658010797101976</v>
       </c>
       <c r="G83">
-        <v>-5.816983891540511</v>
+        <v>-6.222760768834521</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.968908342284983</v>
       </c>
       <c r="E84">
-        <v>-18.69105211966662</v>
+        <v>-20.60217683427969</v>
       </c>
       <c r="F84">
-        <v>-3.443207832704586</v>
+        <v>-2.823538484998985</v>
       </c>
       <c r="G84">
-        <v>-5.81631185079604</v>
+        <v>-6.601437520344055</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.967621216973073</v>
       </c>
       <c r="E85">
-        <v>-18.27128974999962</v>
+        <v>-21.34641795201829</v>
       </c>
       <c r="F85">
-        <v>-3.001245658819355</v>
+        <v>-2.801670413932481</v>
       </c>
       <c r="G85">
-        <v>-4.726039956711242</v>
+        <v>-6.106610278589191</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.970470479329347</v>
       </c>
       <c r="E86">
-        <v>-19.7547997210164</v>
+        <v>-21.98476523356153</v>
       </c>
       <c r="F86">
-        <v>-2.881573905239118</v>
+        <v>-2.686401433098124</v>
       </c>
       <c r="G86">
-        <v>-5.239618128400538</v>
+        <v>-6.16157526617771</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.990548933120253</v>
       </c>
       <c r="E87">
-        <v>-22.90753238210452</v>
+        <v>-23.4199156306504</v>
       </c>
       <c r="F87">
-        <v>-3.385169927362244</v>
+        <v>-2.884200658273396</v>
       </c>
       <c r="G87">
-        <v>-5.250337674856699</v>
+        <v>-6.734375787019029</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.024527471165299</v>
       </c>
       <c r="E88">
-        <v>-23.00722220890938</v>
+        <v>-24.22294539795658</v>
       </c>
       <c r="F88">
-        <v>-3.430732619618425</v>
+        <v>-3.000242505894565</v>
       </c>
       <c r="G88">
-        <v>-6.37492999454712</v>
+        <v>-6.05600859002143</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.072509937966713</v>
       </c>
       <c r="E89">
-        <v>-24.40129934674867</v>
+        <v>-25.76852716219649</v>
       </c>
       <c r="F89">
-        <v>-3.285808914131249</v>
+        <v>-3.19805167147867</v>
       </c>
       <c r="G89">
-        <v>-5.513592256139543</v>
+        <v>-6.868161553352056</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.143221344152057</v>
       </c>
       <c r="E90">
-        <v>-23.95469671163821</v>
+        <v>-26.99589305791741</v>
       </c>
       <c r="F90">
-        <v>-3.293630359148482</v>
+        <v>-3.379886600067189</v>
       </c>
       <c r="G90">
-        <v>-6.329866848666561</v>
+        <v>-6.597729709340071</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.227786419036718</v>
       </c>
       <c r="E91">
-        <v>-25.59329786046969</v>
+        <v>-28.06958518818804</v>
       </c>
       <c r="F91">
-        <v>-3.375974220823767</v>
+        <v>-3.309030537533928</v>
       </c>
       <c r="G91">
-        <v>-6.444348823960098</v>
+        <v>-7.174158588092431</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.328170533350644</v>
       </c>
       <c r="E92">
-        <v>-29.4104482279632</v>
+        <v>-29.7449032042737</v>
       </c>
       <c r="F92">
-        <v>-4.018883416014908</v>
+        <v>-3.350996458527153</v>
       </c>
       <c r="G92">
-        <v>-6.631891228759811</v>
+        <v>-7.200838274593417</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.446714923391639</v>
       </c>
       <c r="E93">
-        <v>-30.32197570401915</v>
+        <v>-31.68121529131744</v>
       </c>
       <c r="F93">
-        <v>-4.011881226359044</v>
+        <v>-3.538007855015767</v>
       </c>
       <c r="G93">
-        <v>-6.332386173821947</v>
+        <v>-7.0949902020663</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.568102098806607</v>
       </c>
       <c r="E94">
-        <v>-33.36837526693316</v>
+        <v>-33.4129105445616</v>
       </c>
       <c r="F94">
-        <v>-3.789638535861965</v>
+        <v>-3.398136362318265</v>
       </c>
       <c r="G94">
-        <v>-7.66814495128032</v>
+        <v>-7.015113359294765</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.69448380587206</v>
       </c>
       <c r="E95">
-        <v>-32.43750667839045</v>
+        <v>-34.93217961057994</v>
       </c>
       <c r="F95">
-        <v>-3.967441800301059</v>
+        <v>-3.822879263001503</v>
       </c>
       <c r="G95">
-        <v>-7.642282969527534</v>
+        <v>-7.338576832300334</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.818546650688076</v>
       </c>
       <c r="E96">
-        <v>-35.10707606946718</v>
+        <v>-37.4073484052184</v>
       </c>
       <c r="F96">
-        <v>-4.259918449411897</v>
+        <v>-3.96255111915493</v>
       </c>
       <c r="G96">
-        <v>-7.29094801362684</v>
+        <v>-7.169878052710153</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.921461677544397</v>
       </c>
       <c r="E97">
-        <v>-36.3764775251643</v>
+        <v>-38.6682974641802</v>
       </c>
       <c r="F97">
-        <v>-4.623683568840258</v>
+        <v>-4.140145635008519</v>
       </c>
       <c r="G97">
-        <v>-7.482145260701908</v>
+        <v>-7.877500540638291</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.001126074391475</v>
       </c>
       <c r="E98">
-        <v>-38.44313947228183</v>
+        <v>-40.73523111973819</v>
       </c>
       <c r="F98">
-        <v>-4.898442267572618</v>
+        <v>-4.117431800823756</v>
       </c>
       <c r="G98">
-        <v>-8.403549537374023</v>
+        <v>-8.148270060295282</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.045701223691315</v>
       </c>
       <c r="E99">
-        <v>-41.99938860253442</v>
+        <v>-42.71139604228642</v>
       </c>
       <c r="F99">
-        <v>-5.03059089097382</v>
+        <v>-4.271958769611587</v>
       </c>
       <c r="G99">
-        <v>-7.498115332383352</v>
+        <v>-9.114833488668594</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.035740077088796</v>
       </c>
       <c r="E100">
-        <v>-43.27087542051208</v>
+        <v>-45.11090082896772</v>
       </c>
       <c r="F100">
-        <v>-4.743260888536575</v>
+        <v>-4.247618021847727</v>
       </c>
       <c r="G100">
-        <v>-8.757019795147546</v>
+        <v>-8.818576078904755</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.974930893482269</v>
       </c>
       <c r="E101">
-        <v>-45.49035298725544</v>
+        <v>-47.10074627149314</v>
       </c>
       <c r="F101">
-        <v>-4.627070763150305</v>
+        <v>-4.355653698520839</v>
       </c>
       <c r="G101">
-        <v>-8.37553239047517</v>
+        <v>-8.806671357145536</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.847386784346135</v>
       </c>
       <c r="E102">
-        <v>-48.90970521613766</v>
+        <v>-48.29264515878598</v>
       </c>
       <c r="F102">
-        <v>-5.031113590804987</v>
+        <v>-4.864177678323219</v>
       </c>
       <c r="G102">
-        <v>-8.851516007020503</v>
+        <v>-9.729965955320573</v>
       </c>
     </row>
   </sheetData>
